--- a/tabelas_classes_excel/Tabela_3-12_O_Ladino.xlsx
+++ b/tabelas_classes_excel/Tabela_3-12_O_Ladino.xlsx
@@ -904,9 +904,6 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-    </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
@@ -1485,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1538,31 +1535,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2240,1325 +2212,6 @@
       <c r="F23" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Religião: Mesmo não sendo famosos por sua devoção, os ladinos normalmente</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Habilidades: A Destreza forn</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adoram Olidammara (deusa dos ladrões). Os ladinos Maus podem adorar secreta-</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>armaduras leves. A Destreza, a I</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>mente Nerull (deus da morte) ou Erythnul (deus da matança). No entanto, como os</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>maioria das perícias do ladino.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ladinos são muito diferentes, podem venerar outras divindades ou nenhuma.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pontos de perícia adicionais, se</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>História: Alguns ladinos são oficialmente iniciados em uma organização de</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Tendência: Qualquer uma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ladinos ou “guilda de ladrões”. Entretanto, a maioria aprende sozinha ou com um</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Dado de Vida: d6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>mentor independente. Muitas vezes, um ladino experiente precisa de ajudantes para</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>realizar um golpe ou para vigiar sua retaguarda. Ele recruta um novato entusiasmado</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Perícias de Classe</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>e ávido por aprender em troca de trabalho. Com o tempo, o aprendiz estará pronto</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>As perícias de classe de um</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>para prosseguir sozinho – talvez porque seu mentor foi preso ou porque abandonou</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>são: Abrir Fechaduras (Des), Acr</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>seu mentor e precisa de mais “espaço”.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Avaliação (Int);</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Os ladinos não se consideram companheiros, a menos que sejam membros da</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Blefar (Car), Conhecimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>mesma guilda ou pupilos do mesmo mestre. Na verdade, os ladinos confiam ainda</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>(Car), Disfarces (Car)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>menos em outros ladinos do que nos demais. Eles não são bobos.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Falsi</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Raças: Adaptáveis e muitas vezes sem escrúpulos, os humanos se tornam</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Nat</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ladinos com facilidade. Os halflings, meio-elfos e elfos também são capazes</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Of</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>de seguir essa carreira. Os ladinos anões e gnomos, embora raros, são</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>famosos por sua perícia com trancas e armadilhas. Os ladinos meio-orcs</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>costumam ser muito violentos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Existem muitos ladinos entre os humanóides brutais, especialmente</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>goblins e bugbears. Porém, todos que aprendem suas artes em terras</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>per</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>selvagens não costumam ter experiência com mecanismos complexos,</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>como armadilhas e trancas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Outras Classes: Os ladinos amam e odeiam trabalhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>com membros de outras classes. É excelente ser protegi-</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>do por guerreiros e contar com o apoio dos</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>magos. Contudo, muitas vezes os ladinos</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>desejam que todos sejam tão reservados,</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>astutos e pacientes quanto eles. Os ladinos</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>são particularmente cautelosos com os pa-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ladinos, e se esforçam para demonstrar sua</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>utilidade quando o contato com os paladinos</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>é inevitável.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Função: A função de um ladino em um</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>grupo pode variar drasticamente, baseado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>em sua seleção de perícias – do char-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>latão carismático ao ladrão esperto ou</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>combatente ágil – embora grande parte</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>dos ladinos compartilhe determinadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>características. Eles não são capazes de</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>combates corporais prolongados, por-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>tanto se concentram nas oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>de ataques furtivos e nos ataques â distân-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cia. A furtividade e a habilidade de encon-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>trar armadilhas do ladino os tornam os</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>melhores batedores do mundo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>INFORMAÇÕES DE JOGO</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Lidda</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>8-5:</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Os ladinos possuem as seguintes estatísticas de jogo.</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>8-6 Modif</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>situações em que o oponente é flanqueado pelo ladino ou perde seu bônus de</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>um teste de resistência de Refl</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Destreza na CA).</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>utilizar a habilidade Evasão do</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Os ataques à distância somente funcionam como ataques furtivos quando o</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Evasão Aprimorada (Ext):</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>alvo estiver num raio de 9 m. O ladino não é capaz de atingir com precisão a uma</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>o personagem se tornar alvo de</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>distância maior.</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Reflexos para reduzir o dano à</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Usando um bastão ou um ataque desarmado, é possível realizar um ataque</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>de fogo), ele não sofrerá qualq</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>furtivo que causa dano por contusão, em vez de dano letal. Não é possível usar uma</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>metade do dano mesmo se fracass</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>arma normal para causar dano por contusão em um ataque furtivo, nem mesmo</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ou imobilizado) não recebe os b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>sofrendo -4 de penalidade, pois é necessário utilizar a arma da melhor forma possível</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Oportunismo (Ext): Uma ve</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>para desferir um ataque furtivo (veja Dano por Contusão).</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>de oportunidade contra um inimi</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>O ataque furtivo somente afeta criaturas vivas e de anatomia compreensível</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>personagem. Esse ataque é consi</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>– mortos-vivos, constructos, limos, plantas e criaturas incorpóreas não têm áreas</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>ladino naquela rodada. Mesmo qu</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>vitais para serem atingidas. Toda criatura imune a sucessos decisivos também não</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>não será possível utilizar essa</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>é vulnerável a ataques furtivos. O ladino precisa enxergar sua vítima com clareza</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Maestria em Perícia: O la</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>suficiente para reconhecer um ponto vital e atingi-lo. O ladino não é capaz de usar</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>perícias e capaz de realizar as</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>o ataque furtivo contra uma criatura camuflada ou se estiver atacando os membros</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>as situações mais adversas. Qua</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>de uma criatura cujas áreas vitais estejam fora de alcance.</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>quantidade de perícias equivale</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Encontrar Armadilhas: Os ladinos (e apenas eles) podem usar a perícia Procurar</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>que realizar um teste dessas pe</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>para encontrar armadilhas quando a Classe de Dificuldade é superior a 20. Encontrar</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>distrações que normalmente lhe</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>uma armadilha mundana terá CD 20 ou superior se estiver bem escondida. Encontrar</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>essa habilidade especial mais d</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>uma armadilha mágica terá CD 25 + nível da magia utilizada na sua criação.</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ocasião.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Os ladinos (e apenas eles) podem usar a perícia Operar Mecanismo para de-</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Mente Escorregadia (Ext):</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>sarmar armadilhas mágicas. Uma armadilha mágica terá CD 25 + 0 nível da magia</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>evitar efeitos mágicos que poss</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>utilizada na criação.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Sempre que um ladino com Mente</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Um ladino que obtenha um sucesso com uma margem igual ou superior a 10</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>efeito de encantamento e fracas</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>para desativar uma armadilha conseguirá estudá-la, entender seu funcionamento e</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>novo teste, com a mesma CD, apó</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>superá-la (junto com seus companheiros) sem desarmá-la.</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>oportunidade adicional para rea</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Evasão (Ext): Um ladino de 2° nível ou superior é capaz de evitar ataques má-</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Talento: Um ladino pode e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>gicos ou incomuns por meio de sua agilidade extraordinária. Sempre que o ladino</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>habilidade especial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>se tornar alvo de um ataque que permita um teste de resistência de Reflexos para</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>reduzir o dano à metade (como um sopro de dragão ou uma bola de fogo), ele não</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Conjunto Inicial para Ladino Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>sofrerá qualquer dano se obtiver sucesso no teste de resistência. A evasão somente</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Armadura: Corselete de cou</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>poderá ser utilizada quando o ladino estiver sem armadura ou usando uma armadura</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Armas: Espada curta (1d4,</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>leve. Um ladino indefeso (inconsciente, paralisado ou imobilizado) não recebe os</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Besta leve (1d8, dec. 19-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>benefícios dessa habilidade.</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Adaga (1d3, dec. 19-20/ x</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sentir Armadilhas (Ext): A partir do 3° nível, o ladino adquire um senso</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Seleção de Perícias: Escol</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>intuitivo que o adverte do perigo das armadilhas, concedendo +1 de bônus nos</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>a 8 + modificador de Inteligênc</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>testes de resistência de Reflexos realizados para evitar armadilhas e +1 de bônus de</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>esquiva na CA contra ataques desferidos por armadilhas. Esse bônus aumenta em</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Perícia</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>+1 a cada três níveis subseqüentes (6°, 9°, 12°, 15° e 18° nível). A habilidade sentir</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Blefar</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>armadilhas de diversas classes se acumula.</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Escalar</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Esquiva Sobrenatural (Ext): A partir do 4° nível, o ladino adquire a habilidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Esconder-se</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>intuitiva de reagir ao perigo antes que seus sentidos consigam identificar a ameaça.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Ele conserva seu bônus de Destreza na CA (se houver), mesmo em situações de</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Operar Mecanismo</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>surpresa ou contra os ataques de um oponente invisível. No entanto, ele ainda perde</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Ouvir</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>seu bônus de Destreza na CA quando estiver imobilizado.</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Prestidigitação</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Caso o ladino tenha a habilidade esquiva sobrenatural de uma classe diferente</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Abrir Fechaduras</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>(como um ladino com dois níveis de bárbaro, por exemplo), ele automaticamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Decifrar Escrita</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>adquire esquiva sobrenatural aprimorada (descrita abaixo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Esquiva Sobrenatural Aprimorada (Ext): A partir do 8° nível, o ladino não</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Furtividade</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>poderá mais ser flanqueado, pois reagirá aos adversários das suas laterais com a</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Intimidação</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>mesma facilidade que reagiria a somente um atacante. Essa defesa impede que um</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Observar</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ladino realize um ataque furtivo quando estiver flanqueando o personagem, a menos</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Procurar</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>que o atacante tenha (no mínimo) 4 níveis de ladino acima do nível de classe atual</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Usar Instrumento Mágico</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>do personagem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Caso o ladino tenha a habilidade esquiva sobrenatural de uma classe diferente</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>(veja acima), ele automaticamente adquire esquiva sobrenatural aprimorada. Os</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Talento: Iniciativa Aprimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>níveis das classes que concedem a esquiva sobrenatural se acumulam para determinar</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Equipamento: Mochila com c</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>o nível mínimo dos ladinos capazes de flanquear o personagem.</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>saco, pederneira e isqueiro, in</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Habilidades Especiais: A partir do 10° nível e a cada três níveis subseqüentes</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>óleo. Caixa com 10 virotes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>(13°, 16° e 19°), o ladino adquire uma habilidade especial, a escolha do jogador,</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Dinheiro: 4d4 PO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>dentre as seguintes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Ataque lncapacitante (Ext): Um ladino com essa habilidade especial é capaz de</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>realizar um ataque furtivo com tamanha precisão que o golpe enfraquece e debilita</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>a vitima. Um oponente atingido por um desses ataques furtivos também sofre 2</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Algumas palavras ininteligí</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>pontos de dano em Força. Os pontos de habilidades perdidos serão recuperados</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>machado de guerra quando profer</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>naturalmente, à razão de i ponto por dia para cada habilidade.</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>fazem a magia parecer fácil, ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Amortecer Impacto (Ext): Quando sofrer um ataque letal, o ladino será capaz de</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>seu grimório, preparando cada m</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>amortecer o impacto do golpe, reduzindo a quantidade de dano sofrida. Uma vez por</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>aprendendo as artes arcanas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>dia, durante o combate, quando os pontos de vida do ladino seriam reduzidos a 0 ou</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Os magos dependem de estudo</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>menos devido a um ataque com armas ou outro golpe, mas não devido a habilidades</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>tomos antigos, debatendo teoria</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>mágicas, o personagem pode tentar amortecer esse impacto. Para usar essa habilidade,</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>magias sempre que possível. Par</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>o ladino deve realizar um teste de resistência de Reflexos (CD = dano sofrido). Se</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>complexa, embora gratificante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>obtiver sucesso, sofrerá apenas metade do dano; se fracassar, sofrerá todo o dano.</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Aventuras: Os magos conduze</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Ele deve estar ciente do golpe e ser capaz de reagir para realizar o amortecimento</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>e, quando estão bem preparados,</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>– caso não possa usar seu bônus de Destreza na CA, não conseguirá utilizar essa</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>devastadora. Quando são apanhad</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>habilidade. Como esse efeito, normalmente, não permite que o personagem realize</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>buscam conhecimento, poder e re</t>
         </is>
       </c>
     </row>
